--- a/outputs/evaluation/decision/v1/CF_M01/run_2/CF_M01_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_2/CF_M01_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,101 +471,351 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Amazon S3 service is a necessary service to be able to develop a data lake, since this service allows us to store any element that is needed.</t>
+          <t>Com a framework es farà ús de NestJS [2], amb el llenguatge Typescript [3], i per la infraestructura es farà ús dels serveis cloud d’AWS [4]. Aquestes tecnologies són les mateixes de les quals s’utilitzen actualment a l’empresa de Waapiti.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_03, C_04</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_12, AU_16</t>
+          <t>AU_13, AU_14, P_01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12f. Capacity; 12g. Scalability</t>
+          <t>15a. Access</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cloud Storage Service; Amazon S3</t>
+          <t>NestJS; TypeScript; Client-Server</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD06</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6754</v>
+        <v>0.6915</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor. En aquest tipus d’arquitectura el client és qui realitza les peticions a un servidor, que les processa i retorna la resposta al client. En el nostre cas, el client és l’usuari de la plataforma i el servidor és el software que s’encarrega de processar les peticions de l’usuari.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_01, AU_02, P_01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Client; Backend; Client-Server</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6753</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP [26] i el model de REST API.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_23, P_01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HTTP; Client-Server</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6841</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_03, AU_04, AU_05, P_02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Presentation Layer; Business Layer; Data Layer; Layered Architecture</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6347</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents. L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C_02, C_03, C_04, C_05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_03, AU_04, AU_05, AU_06, AU_07, AU_08, AU_11, AU_12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12d. Availability and reliability; 12f. Capacity; 12g. Scalability; 15a. Access</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Presentation Layer; Business Layer; Data Layer; API Gateway Service; Core Service; Analytical Module Service; Database; Cloud Storage Service</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7478</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>AD_07</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>This service, being a serverless service, means that it is not necessary to manage the infrastructure when there is an increase in the set of data and users.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C_01, Scalability</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>12a. Speed and latency; Scalability</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Amazon Athena</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Com es pot observar en la figura 9.1 la comunicació entre el servei de l’Api Gateway és mitjançant el protocol de comunicació TCP [29].</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AU_06, AU_07, AU_08, AU_09, AU_10, AU_24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>API Gateway Service; Core Service; Analytical Module Service; Player API Service; Web Socket Service; TCP</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>CF_M01_AD02</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>0.6661</v>
+      <c r="J7" t="n">
+        <v>0.6289</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aquesta base de dades està implementada en el servei RDS [30], que és un servei de base de dades relacional distribuït d’AWS.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AU_11, AU_15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Database; AWS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.627</v>
       </c>
     </row>
   </sheetData>
